--- a/Micron_Comparison.xlsx
+++ b/Micron_Comparison.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="2" documentId="8_{9EB82E95-7E40-418F-AC3B-FEFD46FB055C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2551FA75-01DE-4223-8071-EC1179AC14CD}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="1740" windowWidth="19200" windowHeight="11170" xr2:uid="{7C4B40AD-3E23-4794-BA52-E9F2AA549848}"/>
+    <workbookView xWindow="4280" yWindow="3120" windowWidth="19200" windowHeight="11170" xr2:uid="{7C4B40AD-3E23-4794-BA52-E9F2AA549848}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -124,6 +124,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
